--- a/sample_output/invoice_tracker.xlsx
+++ b/sample_output/invoice_tracker.xlsx
@@ -473,7 +473,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-06-13 02:18</t>
+          <t>2026-06-16 21:44</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -511,7 +511,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-06-13 02:18</t>
+          <t>2026-06-16 21:44</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -549,7 +549,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-06-13 02:18</t>
+          <t>2026-06-16 21:44</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -564,7 +564,7 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>2026-09-06</t>
+          <t>2026-06-09</t>
         </is>
       </c>
       <c r="E4" t="n">
@@ -585,7 +585,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-06-13 02:18</t>
+          <t>2026-06-16 21:44</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -623,7 +623,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-06-13 02:18</t>
+          <t>2026-06-16 21:44</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -661,7 +661,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-06-13 02:18</t>
+          <t>2026-06-16 21:44</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -699,7 +699,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-06-13 02:18</t>
+          <t>2026-06-16 21:44</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
